--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/7836-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/7836-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44758A7F-45AB-42A0-8CD5-669915EF8B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6368EE6-22DB-4661-9FB1-9E1B530F3018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{AB28D5C3-4BFF-4FEA-A3AC-877222119744}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2D884F38-8050-4DDD-BB89-B474EDBDAC68}"/>
   </bookViews>
   <sheets>
     <sheet name="7836-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1525,18 +1525,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A61E17-6E0D-4140-8909-686C56B61777}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3A0441-501A-45AA-9ADB-573BA42B87A0}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.21875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="17" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1690,7 +1690,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1770,7 +1770,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>27</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="54"/>
       <c r="B10" s="22" t="s">
         <v>30</v>
@@ -1958,7 +1958,7 @@
       <c r="Q10" s="58"/>
       <c r="R10" s="58"/>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="63" t="s">
         <v>33</v>
       </c>
